--- a/data/27April-Tigers-v-Gold_Diggers.xlsx
+++ b/data/27April-Tigers-v-Gold_Diggers.xlsx
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O135"/>
   <sheetData>
     <row r="1">
@@ -444,8 +444,10 @@
       <c r="D15" t="s">
         <v>22</v>
       </c>
-      <c r="E15" t="s">
-        <v>23</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
       </c>
       <c r="I15" t="s">
         <v>24</v>
@@ -701,8 +703,10 @@
       <c r="D40" t="s">
         <v>29</v>
       </c>
-      <c r="E40" t="s">
-        <v>35</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UCDCLM</t>
+        </is>
       </c>
       <c r="I40" t="s">
         <v>17</v>
@@ -781,8 +785,10 @@
       <c r="D47" t="s">
         <v>29</v>
       </c>
-      <c r="E47" t="s">
-        <v>39</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I47" t="s">
         <v>24</v>
@@ -859,8 +865,10 @@
       <c r="D53" t="s">
         <v>29</v>
       </c>
-      <c r="E53" t="s">
-        <v>44</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DCLCUC</t>
+        </is>
       </c>
       <c r="I53" t="s">
         <v>17</v>
@@ -988,8 +996,10 @@
       <c r="D62" t="s">
         <v>29</v>
       </c>
-      <c r="E62" t="s">
-        <v>39</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I62" t="s">
         <v>24</v>
